--- a/tests/data_golden/markers.expected.xlsx
+++ b/tests/data_golden/markers.expected.xlsx
@@ -115,10 +115,10 @@
     <t>b</t>
   </si>
   <si>
-    <t>No.1: a</t>
-  </si>
-  <si>
-    <t>No.2: b</t>
+    <t xml:space="preserve">No.1: a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No.2: b</t>
   </si>
 </sst>
 </file>
